--- a/artfynd/A 15977-2024 artfynd.xlsx
+++ b/artfynd/A 15977-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1719,6 +1719,116 @@
       <c r="AY10" t="inlineStr">
         <is>
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>120327855</v>
+      </c>
+      <c r="B11" t="n">
+        <v>90580</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Halån, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>568045</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7014961</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
     </row>

--- a/artfynd/A 15977-2024 artfynd.xlsx
+++ b/artfynd/A 15977-2024 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>104025335</v>
+        <v>104025295</v>
       </c>
       <c r="B2" t="n">
-        <v>77177</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>568411.2044413907</v>
+        <v>568358</v>
       </c>
       <c r="R2" t="n">
-        <v>7015169.818722341</v>
+        <v>7015210</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,15 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>104025284</v>
+        <v>104025297</v>
       </c>
       <c r="B3" t="n">
-        <v>78072</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>568445.5138691869</v>
+        <v>568451</v>
       </c>
       <c r="R3" t="n">
-        <v>7015211.092302547</v>
+        <v>7015199</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,7 +856,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -876,7 +866,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,37 +897,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>104025342</v>
+        <v>104025335</v>
       </c>
       <c r="B4" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -947,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>568507.0460559996</v>
+        <v>568411</v>
       </c>
       <c r="R4" t="n">
-        <v>7015160.143335289</v>
+        <v>7015170</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -982,7 +967,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -992,7 +977,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,15 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>104025274</v>
+        <v>120327855</v>
       </c>
       <c r="B5" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1039,34 +1019,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hopmyran, Jmt</t>
+          <t>Halån, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>568325.6101275174</v>
+        <v>568045</v>
       </c>
       <c r="R5" t="n">
-        <v>7015185.570748897</v>
+        <v>7014961</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,22 +1076,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-08-15</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>12:58</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-08-15</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>12:58</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1117,42 +1090,33 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Tall</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Ulrika Westling</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
+          <t>Ulrika Westling</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+          <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>104025321</v>
+        <v>104025342</v>
       </c>
       <c r="B6" t="n">
-        <v>76909</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1160,21 +1124,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6437</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1184,10 +1148,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>568418.5171188154</v>
+        <v>568507</v>
       </c>
       <c r="R6" t="n">
-        <v>7015207.815626611</v>
+        <v>7015160</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1219,7 +1183,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1229,7 +1193,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1260,37 +1224,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>104025297</v>
+        <v>104025274</v>
       </c>
       <c r="B7" t="n">
-        <v>77177</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1300,10 +1259,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>568451.6244767607</v>
+        <v>568326</v>
       </c>
       <c r="R7" t="n">
-        <v>7015199.509391105</v>
+        <v>7015186</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1335,7 +1294,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1345,7 +1304,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1356,6 +1315,11 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Tall</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1376,15 +1340,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>104025299</v>
+        <v>104025321</v>
       </c>
       <c r="B8" t="n">
-        <v>77259</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78730</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1392,21 +1351,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>6437</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1416,10 +1375,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>568508.6497975006</v>
+        <v>568418</v>
       </c>
       <c r="R8" t="n">
-        <v>7015211.984438109</v>
+        <v>7015208</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1451,7 +1410,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1461,7 +1420,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1492,15 +1451,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>104025322</v>
+        <v>104025299</v>
       </c>
       <c r="B9" t="n">
-        <v>78072</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1508,21 +1462,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1532,10 +1486,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>568250.8074310302</v>
+        <v>568508</v>
       </c>
       <c r="R9" t="n">
-        <v>7015181.731952598</v>
+        <v>7015212</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1567,7 +1521,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1577,7 +1531,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1608,15 +1562,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>104025295</v>
+        <v>104025284</v>
       </c>
       <c r="B10" t="n">
-        <v>77177</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79917</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1624,21 +1573,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1648,10 +1597,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>568358.4705387912</v>
+        <v>568445</v>
       </c>
       <c r="R10" t="n">
-        <v>7015210.144281539</v>
+        <v>7015211</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1683,7 +1632,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1693,7 +1642,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1724,15 +1673,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120327855</v>
+        <v>104025322</v>
       </c>
       <c r="B11" t="n">
-        <v>90636</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79917</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1740,37 +1684,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>229821</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Halån, Jmt</t>
+          <t>Hopmyran, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>568045</v>
+        <v>568251</v>
       </c>
       <c r="R11" t="n">
-        <v>7014961</v>
+        <v>7015182</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1797,12 +1738,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2022-08-15</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2022-08-15</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1811,24 +1762,23 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
+          <t>Via Johan Staaf</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>SCA Skog Naturvärdesinventering</t>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
     </row>

--- a/artfynd/A 15977-2024 artfynd.xlsx
+++ b/artfynd/A 15977-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104025295</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104025297</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1003,6 +1018,11 @@
       <c r="AY4" t="inlineStr">
         <is>
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104025335</t>
         </is>
       </c>
     </row>
@@ -1110,6 +1130,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120327855</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1221,6 +1246,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104025342</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1337,6 +1367,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104025274</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1448,6 +1483,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104025321</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1559,6 +1599,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104025299</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1670,6 +1715,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104025284</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1781,8 +1831,25 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104025322</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>